--- a/全量数据/全球黄金ETF流量.xlsx
+++ b/全量数据/全球黄金ETF流量.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周度数据" sheetId="1" r:id="Rbaeb9c3fbe8e4e22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度数据" sheetId="2" r:id="R2ed9f0620df54c14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="周度数据" sheetId="1" r:id="Rfde898add1dd4555"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度数据" sheetId="2" r:id="Rb6a134d21fce48bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15045,19 +15045,51 @@
         <x:v>1009292895.48</x:v>
       </x:c>
       <x:c r="H460" s="7" t="n">
-        <x:v>242548970.35</x:v>
+        <x:v>252392750.35</x:v>
       </x:c>
       <x:c r="I460" s="7" t="n">
         <x:v>652895283.47</x:v>
       </x:c>
       <x:c r="J460" s="7" t="n">
         <x:v>-958900</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="461">
+      <x:c r="A461" s="8" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="B461" s="6" t="n">
+        <x:v>-13.09578019</x:v>
+      </x:c>
+      <x:c r="C461" s="6" t="n">
+        <x:v>4.33378151</x:v>
+      </x:c>
+      <x:c r="D461" s="6" t="n">
+        <x:v>0.21735631</x:v>
+      </x:c>
+      <x:c r="E461" s="6" t="n">
+        <x:v>0.44601201</x:v>
+      </x:c>
+      <x:c r="F461" s="7" t="n">
+        <x:v>4092.25</x:v>
+      </x:c>
+      <x:c r="G461" s="7" t="n">
+        <x:v>-1691401004.2</x:v>
+      </x:c>
+      <x:c r="H461" s="7" t="n">
+        <x:v>455213045.76</x:v>
+      </x:c>
+      <x:c r="I461" s="7" t="n">
+        <x:v>21351291.75</x:v>
+      </x:c>
+      <x:c r="J461" s="7" t="n">
+        <x:v>7484900</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46e8b526d21a4310"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2acf5557791442c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24197,7 +24229,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3278ed952e64f5f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74479233309c4ebf"/>
   </x:tableParts>
 </x:worksheet>
 </file>